--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -115,11 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"type":"kill","id":"rogue","count":3},
-{"type":"final","des":"跟 musk 回報"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>musk_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -129,11 +124,6 @@
   </si>
   <si>
     <t>melanie_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"type":"kill","id":"rogue","count":3},
-{"type":"final","des":"跟 melanie 回報"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -150,11 +140,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"type":"kill","id":"rogue","count":3},
-{"type":"final","des":"跟 karen 回報"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>xi_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -170,6 +155,21 @@
   <si>
     <t>{"type":"kill","id":"rogue","count":3},
 {"type":"final","des":"跟 macron 回報"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"type":"kill","id":"rogue","count":3,"nid":"forest-01"},
+{"des":"跟 musk 回報","nid":"village-01","refs":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"type":"kill","id":"rogue","count":3},
+{"des":"跟 melanie 回報","refs":1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"type":"kill","id":"rogue","count":3,"nid":"forest-01"},
+{"des":"跟 karen 回報","refs":[0],"nid":"village-01"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -534,7 +534,7 @@
     <col min="2" max="2" width="24.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="38.88671875" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="43.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="57" style="1" customWidth="1"/>
     <col min="6" max="6" width="68.88671875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="8.88671875" style="1"/>
   </cols>
@@ -561,7 +561,7 @@
     </row>
     <row r="2" spans="1:6" ht="62.4">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>23</v>
@@ -573,7 +573,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>18</v>
@@ -581,7 +581,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
@@ -595,7 +595,7 @@
     </row>
     <row r="5" spans="1:6" ht="62.4">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>23</v>
@@ -607,7 +607,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>18</v>
@@ -615,7 +615,7 @@
     </row>
     <row r="7" spans="1:6" ht="62.4">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>23</v>
@@ -627,7 +627,7 @@
         <v>21</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>18</v>
@@ -635,7 +635,7 @@
     </row>
     <row r="9" spans="1:6" ht="62.4">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>23</v>
@@ -647,7 +647,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>18</v>
@@ -655,7 +655,7 @@
     </row>
     <row r="11" spans="1:6" ht="62.4">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>23</v>
@@ -667,7 +667,7 @@
         <v>21</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>18</v>
@@ -675,7 +675,7 @@
     </row>
     <row r="13" spans="1:6" ht="62.4">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>23</v>
@@ -687,7 +687,7 @@
         <v>21</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>18</v>

--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -159,17 +159,17 @@
   </si>
   <si>
     <t>{"type":"kill","id":"rogue","count":3,"nid":"forest-01"},
-{"des":"跟 musk 回報","nid":"village-01","refs":0}</t>
+{"des":"跟 karen 回報","refs":[0],"nid":"village-01"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"type":"kill","id":"rogue","count":3,"nid":"forest-01"},
+{"des":"跟 musk 回報","nid":"village-01","refs":[0]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{"type":"kill","id":"rogue","count":3},
-{"des":"跟 melanie 回報","refs":1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"type":"kill","id":"rogue","count":3,"nid":"forest-01"},
-{"des":"跟 karen 回報","refs":[0],"nid":"village-01"}</t>
+{"des":"跟 melanie 回報","refs":[0]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -573,7 +573,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>18</v>
@@ -607,7 +607,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>18</v>
@@ -647,7 +647,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>18</v>

--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -159,17 +159,33 @@
   </si>
   <si>
     <t>{"type":"kill","id":"rogue","count":3,"nid":"forest-01"},
-{"des":"跟 karen 回報","refs":[0],"nid":"village-01"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"type":"kill","id":"rogue","count":3,"nid":"forest-01"},
 {"des":"跟 musk 回報","nid":"village-01","refs":[0]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{"type":"kill","id":"rogue","count":3},
 {"des":"跟 melanie 回報","refs":[0]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遺失的劍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Karen 的配劍遺失在北方森林，幫她找回。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"type":"remove","id":"sword_01","count":1,"q":"karen_01"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"type":"find","id":"sword_01","count":1,"q":"karen_01","nid":"forest-01"},
+{"type":"report","des":"跟 karen 回報","refs":[0],"nid":"village-01"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -527,19 +543,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="13.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="24.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="38.88671875" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="57" style="1" customWidth="1"/>
-    <col min="6" max="6" width="68.88671875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="1"/>
+    <col min="5" max="5" width="70.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="45.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="71.109375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -558,8 +575,11 @@
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="62.4">
+      <c r="G1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="62.4">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -573,13 +593,13 @@
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -593,7 +613,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="62.4">
+    <row r="5" spans="1:7" ht="62.4">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -607,13 +627,13 @@
         <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="62.4">
+    <row r="7" spans="1:7" ht="62.4">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -633,27 +653,30 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="62.4">
+    <row r="9" spans="1:7" ht="31.2">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="62.4">
+      <c r="G9" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="62.4">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -673,7 +696,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="62.4">
+    <row r="13" spans="1:7" ht="62.4">
       <c r="A13" s="1" t="s">
         <v>32</v>
       </c>

--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="karen" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="xi" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="49">
   <si>
     <t>//</t>
   </si>
@@ -125,6 +126,42 @@
   </si>
   <si>
     <t>none</t>
+  </si>
+  <si>
+    <t>QX01</t>
+  </si>
+  <si>
+    <t>屠夫的生意經</t>
+  </si>
+  <si>
+    <t>黑森林的野狼氾濫，xi 的肉舖快沒貨了，想找人幫忙獵狼取皮，順便帶個口信給城裡的商人 karen。</t>
+  </si>
+  <si>
+    <t>axe_01</t>
+  </si>
+  <si>
+    <t>前往黑森林狩獵，擊殺野狼 ({current}/{required})</t>
+  </si>
+  <si>
+    <t>剝下狼皮 ({current}/{required})</t>
+  </si>
+  <si>
+    <t>plet</t>
+  </si>
+  <si>
+    <t>set qx01_pelt_ready</t>
+  </si>
+  <si>
+    <t>帶著狼皮去找商人 karen 談談</t>
+  </si>
+  <si>
+    <t>qx01_karen_done</t>
+  </si>
+  <si>
+    <t>step_04</t>
+  </si>
+  <si>
+    <t>任務完成，回去跟 xi 回報</t>
   </si>
 </sst>
 </file>
@@ -157,28 +194,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -201,10 +236,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -221,59 +263,38 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -629,7 +650,7 @@
     <col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -651,188 +672,225 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1" s="4"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="6">
         <v>100</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="6">
         <v>100</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="11"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I3" s="6"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="16" t="s">
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15" t="s">
+      <c r="F7" s="8"/>
+      <c r="G7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="8">
         <v>1</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="16"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
+      <c r="J7" s="8"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15" t="s">
+      <c r="F8" s="8"/>
+      <c r="G8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="8">
         <v>1</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="16"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="17" t="s">
+      <c r="J8" s="8"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18" t="s">
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="19"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -876,9 +934,250 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="47.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6">
+        <v>120</v>
+      </c>
+      <c r="F3" s="6">
+        <v>120</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="8">
+        <v>3</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="8">
+        <v>3</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
 </file>
--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="585" windowWidth="12615" windowHeight="6750"/>
+    <workbookView xWindow="720" yWindow="585" windowWidth="12615" windowHeight="6750" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="karen" state="visible" r:id="rId4"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="48">
   <si>
     <t>//</t>
   </si>
@@ -147,9 +147,6 @@
   </si>
   <si>
     <t>plet</t>
-  </si>
-  <si>
-    <t>set qx01_pelt_ready</t>
   </si>
   <si>
     <t>帶著狼皮去找商人 karen 談談</t>
@@ -205,11 +202,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -634,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" customWidth="1"/>
@@ -650,7 +649,7 @@
     <col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -676,11 +675,8 @@
         <v>7</v>
       </c>
       <c r="I1" s="4"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-    </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -708,12 +704,8 @@
       <c r="I2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>15</v>
       </c>
@@ -734,25 +726,8 @@
         <v>18</v>
       </c>
       <c r="I3" s="6"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -783,11 +758,8 @@
       <c r="J5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
         <v>15</v>
       </c>
@@ -809,11 +781,8 @@
       <c r="J6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-    </row>
-    <row r="7" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
@@ -837,11 +806,8 @@
         <v>21</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>15</v>
       </c>
@@ -865,11 +831,8 @@
         <v>26</v>
       </c>
       <c r="J8" s="8"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
@@ -889,64 +852,6 @@
         <v>30</v>
       </c>
       <c r="J9" s="10"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -956,8 +861,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -971,7 +876,7 @@
     <col min="10" max="10" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -997,7 +902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1026,7 +931,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="47.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" ht="47.25" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>37</v>
       </c>
@@ -1048,8 +953,7 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1081,7 +985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
         <v>37</v>
       </c>
@@ -1099,12 +1003,12 @@
         <v>29</v>
       </c>
       <c r="H6" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
     </row>
-    <row r="7" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>37</v>
       </c>
@@ -1122,16 +1026,14 @@
         <v>43</v>
       </c>
       <c r="H7" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
@@ -1139,13 +1041,13 @@
         <v>30</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
@@ -1154,15 +1056,15 @@
       </c>
       <c r="J8" s="8"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>48</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>36</v>
@@ -1175,7 +1077,6 @@
       </c>
       <c r="J9" s="10"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -47,13 +47,13 @@
     <t>titleKey</t>
   </si>
   <si>
-    <t>reward_gold</t>
-  </si>
-  <si>
-    <t>reward_exp</t>
-  </si>
-  <si>
-    <t>reward_items</t>
+    <t>rewards_gold</t>
+  </si>
+  <si>
+    <t>rewards_exp</t>
+  </si>
+  <si>
+    <t>rewards_items</t>
   </si>
   <si>
     <t>actions_start</t>

--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="50">
   <si>
     <t>//</t>
   </si>
@@ -138,6 +138,12 @@
   </si>
   <si>
     <t>axe_01</t>
+  </si>
+  <si>
+    <t>set QX01</t>
+  </si>
+  <si>
+    <t>rm QX01</t>
   </si>
   <si>
     <t>前往黑森林狩獵，擊殺野狼 ({current}/{required})</t>
@@ -931,7 +937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="47.25" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" ht="47.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>37</v>
       </c>
@@ -950,9 +956,14 @@
       <c r="G3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-    </row>
+      <c r="H3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25"/>
     <row r="5" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
@@ -985,7 +996,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
         <v>37</v>
       </c>
@@ -993,7 +1004,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>28</v>
@@ -1003,12 +1014,12 @@
         <v>29</v>
       </c>
       <c r="H6" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>37</v>
       </c>
@@ -1016,14 +1027,14 @@
         <v>26</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H7" s="8">
         <v>1</v>
@@ -1033,7 +1044,7 @@
       </c>
       <c r="J7" s="8"/>
     </row>
-    <row r="8" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
@@ -1041,13 +1052,13 @@
         <v>30</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
@@ -1056,15 +1067,15 @@
       </c>
       <c r="J8" s="8"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>36</v>

--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="585" windowWidth="12615" windowHeight="6750" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="karen" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="xi" state="visible" r:id="rId5"/>
+    <sheet name="karen" sheetId="1" r:id="rId1"/>
+    <sheet name="xi" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="50">
   <si>
     <t>//</t>
   </si>
@@ -170,21 +170,28 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="微軟正黑體 Light"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -207,13 +214,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -228,44 +235,78 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -302,7 +343,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -638,9 +679,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
@@ -652,10 +693,11 @@
     <col min="8" max="8" width="21.5703125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="20.28515625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -682,7 +724,7 @@
       </c>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -711,7 +753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="31.5" customHeight="1">
       <c r="B3" s="5" t="s">
         <v>15</v>
       </c>
@@ -733,7 +775,7 @@
       </c>
       <c r="I3" s="6"/>
     </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="31.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -765,7 +807,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="31.5" customHeight="1">
       <c r="B6" s="7" t="s">
         <v>15</v>
       </c>
@@ -788,7 +830,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="31.5" customHeight="1">
       <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
@@ -813,7 +855,7 @@
       </c>
       <c r="J7" s="8"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="B8" s="7" t="s">
         <v>15</v>
       </c>
@@ -838,7 +880,7 @@
       </c>
       <c r="J8" s="8"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
@@ -860,15 +902,16 @@
       <c r="J9" s="10"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -882,7 +925,7 @@
     <col min="10" max="10" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="31.5" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -907,8 +950,14 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="31.5" customHeight="1">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -937,7 +986,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="47.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="47.25" customHeight="1">
       <c r="B3" s="5" t="s">
         <v>37</v>
       </c>
@@ -963,8 +1012,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="31.5" customHeight="1">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -996,7 +1044,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="31.5" customHeight="1">
       <c r="B6" s="7" t="s">
         <v>37</v>
       </c>
@@ -1019,7 +1067,7 @@
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="B7" s="7" t="s">
         <v>37</v>
       </c>
@@ -1044,7 +1092,7 @@
       </c>
       <c r="J7" s="8"/>
     </row>
-    <row r="8" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="31.5" customHeight="1">
       <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
@@ -1067,7 +1115,7 @@
       </c>
       <c r="J8" s="8"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
@@ -1089,7 +1137,8 @@
       <c r="J9" s="10"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -1,34 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="585" windowWidth="12615" windowHeight="6750" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="karen" sheetId="1" r:id="rId1"/>
-    <sheet name="xi" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="karen" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="xi" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="50">
-  <si>
-    <t>//</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="58">
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>quest_id</t>
   </si>
   <si>
+    <t>titleKey</t>
+  </si>
+  <si>
+    <t>descKey</t>
+  </si>
+  <si>
+    <t>rewards_gold</t>
+  </si>
+  <si>
+    <t>rewards_exp</t>
+  </si>
+  <si>
+    <t>rewards_items</t>
+  </si>
+  <si>
+    <t>actions_start</t>
+  </si>
+  <si>
+    <t>actions_complete</t>
+  </si>
+  <si>
+    <t>QK01</t>
+  </si>
+  <si>
+    <t>黑森林討伐</t>
+  </si>
+  <si>
+    <t>黑森林的野狼越來越猖獗，長老需要你的幫助。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set QK01_xi ;
+set QK01_map</t>
+  </si>
+  <si>
+    <t>rm QK01_map</t>
+  </si>
+  <si>
     <t>step_id</t>
   </si>
   <si>
-    <t>descKey</t>
-  </si>
-  <si>
     <t>complete_type</t>
   </si>
   <si>
@@ -41,39 +75,6 @@
     <t>complete_required</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>titleKey</t>
-  </si>
-  <si>
-    <t>rewards_gold</t>
-  </si>
-  <si>
-    <t>rewards_exp</t>
-  </si>
-  <si>
-    <t>rewards_items</t>
-  </si>
-  <si>
-    <t>actions_start</t>
-  </si>
-  <si>
-    <t>actions_complete</t>
-  </si>
-  <si>
-    <t>QK01</t>
-  </si>
-  <si>
-    <t>黑森林討伐</t>
-  </si>
-  <si>
-    <t>黑森林的野狼越來越猖獗，長老需要你的幫助。</t>
-  </si>
-  <si>
-    <t>set qk01_start</t>
-  </si>
-  <si>
     <t>conds</t>
   </si>
   <si>
@@ -89,10 +90,10 @@
     <t>flag</t>
   </si>
   <si>
-    <t>qk01_talk_xi</t>
-  </si>
-  <si>
-    <t>rm qk01_talk_xi</t>
+    <t>QK01_talk_xi</t>
+  </si>
+  <si>
+    <t>rm QK01_talk_xi</t>
   </si>
   <si>
     <t>step_02</t>
@@ -140,10 +141,10 @@
     <t>axe_01</t>
   </si>
   <si>
-    <t>set QX01</t>
-  </si>
-  <si>
-    <t>rm QX01</t>
+    <t>set QX01_map</t>
+  </si>
+  <si>
+    <t>rm QX01_map</t>
   </si>
   <si>
     <t>前往黑森林狩獵，擊殺野狼 ({current}/{required})</t>
@@ -155,43 +156,67 @@
     <t>plet</t>
   </si>
   <si>
+    <t>set QX01_karen</t>
+  </si>
+  <si>
     <t>帶著狼皮去找商人 karen 談談</t>
   </si>
   <si>
-    <t>qx01_karen_done</t>
+    <t>QX01_karen_done</t>
   </si>
   <si>
     <t>step_04</t>
   </si>
   <si>
     <t>任務完成，回去跟 xi 回報</t>
+  </si>
+  <si>
+    <t>QX02</t>
+  </si>
+  <si>
+    <t>跑腿的交涉</t>
+  </si>
+  <si>
+    <t>黑森林的野狼問題解決後，xi 想跟 karen 談長期收購狼皮的生意，請你幫忙帶提案去交涉。</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>set QX02_karen</t>
+  </si>
+  <si>
+    <t>帶著提案去找商人 karen 談交涉條件</t>
+  </si>
+  <si>
+    <t>QX02_karen_done</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="微軟正黑體 Light"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
       <charset val="136"/>
-      <scheme val="minor"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <sz val="11"/>
+      <name val="微軟正黑體 Light"/>
     </font>
   </fonts>
   <fills count="6">
@@ -208,24 +233,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -234,116 +259,52 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -679,11 +640,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="57.7109375" style="1" customWidth="1"/>
@@ -693,452 +654,533 @@
     <col min="8" max="8" width="21.5703125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="20.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.5" customHeight="1">
+    <row r="1" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="2" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3">
+        <v>100</v>
+      </c>
+      <c r="F2" s="3">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="31.5" customHeight="1">
-      <c r="B3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="6">
-        <v>100</v>
-      </c>
-      <c r="F3" s="6">
-        <v>100</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="6"/>
-    </row>
-    <row r="5" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="31.5" customHeight="1">
-      <c r="B6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="I5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="31.5" customHeight="1">
-      <c r="B7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="8">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="8">
-        <v>1</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="10"/>
+      <c r="J7" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="4" width="57.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" customWidth="1"/>
+    <col min="1" max="1" width="3" style="6" customWidth="1"/>
+    <col min="2" max="2" width="10" style="6" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="20.28515625" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A1" t="s">
+    <row r="1" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="47.25" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="7">
+        <v>120</v>
+      </c>
+      <c r="F2" s="7">
+        <v>120</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="4" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="5">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="5">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="47.25" customHeight="1">
-      <c r="B3" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="6">
-        <v>120</v>
-      </c>
-      <c r="F3" s="6">
-        <v>120</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="31.5" customHeight="1">
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="8">
-        <v>3</v>
-      </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="8">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="31.5" customHeight="1">
-      <c r="B8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="C7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>47</v>
-      </c>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" ht="35.25" customHeight="1" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="7">
+        <v>100</v>
+      </c>
+      <c r="F10" s="7">
+        <v>100</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" ht="32.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B9" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="D13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="10"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="585" windowWidth="12615" windowHeight="6750" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="karen" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="xi" state="visible" r:id="rId5"/>
+    <sheet name="karen" sheetId="1" r:id="rId1"/>
+    <sheet name="xi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="60">
   <si>
     <t>#</t>
   </si>
@@ -53,170 +53,197 @@
     <t>黑森林的野狼越來越猖獗，長老需要你的幫助。</t>
   </si>
   <si>
-    <t xml:space="preserve">set QK01_xi ;
+    <t>step_id</t>
+  </si>
+  <si>
+    <t>complete_type</t>
+  </si>
+  <si>
+    <t>complete_flag</t>
+  </si>
+  <si>
+    <t>complete_id</t>
+  </si>
+  <si>
+    <t>complete_required</t>
+  </si>
+  <si>
+    <t>conds</t>
+  </si>
+  <si>
+    <t>actions</t>
+  </si>
+  <si>
+    <t>step_01</t>
+  </si>
+  <si>
+    <t>與xi對話了解情況</t>
+  </si>
+  <si>
+    <t>flag</t>
+  </si>
+  <si>
+    <t>step_02</t>
+  </si>
+  <si>
+    <t>前往黑森林，擊殺黑森林的野狼 ({current}/{required})</t>
+  </si>
+  <si>
+    <t>kill</t>
+  </si>
+  <si>
+    <t>wolf</t>
+  </si>
+  <si>
+    <t>step_03</t>
+  </si>
+  <si>
+    <t>收集刀子 ({current}/{required})</t>
+  </si>
+  <si>
+    <t>collect</t>
+  </si>
+  <si>
+    <t>sword_01</t>
+  </si>
+  <si>
+    <t>step_05</t>
+  </si>
+  <si>
+    <t>任務完成，跟 karen 回報任務</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>QX01</t>
+  </si>
+  <si>
+    <t>屠夫的生意經</t>
+  </si>
+  <si>
+    <t>黑森林的野狼氾濫，xi 的肉舖快沒貨了，想找人幫忙獵狼取皮，順便帶個口信給城裡的商人 karen。</t>
+  </si>
+  <si>
+    <t>axe_01</t>
+  </si>
+  <si>
+    <t>set QX01_map</t>
+  </si>
+  <si>
+    <t>前往黑森林狩獵，擊殺野狼 ({current}/{required})</t>
+  </si>
+  <si>
+    <t>剝下狼皮 ({current}/{required})</t>
+  </si>
+  <si>
+    <t>plet</t>
+  </si>
+  <si>
+    <t>帶著狼皮去找商人 karen 談談</t>
+  </si>
+  <si>
+    <t>step_04</t>
+  </si>
+  <si>
+    <t>任務完成，回去跟 xi 回報</t>
+  </si>
+  <si>
+    <t>QX02</t>
+  </si>
+  <si>
+    <t>跑腿的交涉</t>
+  </si>
+  <si>
+    <t>黑森林的野狼問題解決後，xi 想跟 karen 談長期收購狼皮的生意，請你幫忙帶提案去交涉。</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>帶著提案去找商人 karen 談交涉條件</t>
+  </si>
+  <si>
+    <t>QX02_s01_done</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>set QX01_s03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>QX01_s03_done</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rm QX01_s03 ;
+rm QX01_s03_done</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rm QX01_map</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>QK01_s01_done</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>set QK01_s01 ;
 set QK01_map</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rm QK01_s01 ;
+rm QK01_s01_done</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>rm QK01_map</t>
-  </si>
-  <si>
-    <t>step_id</t>
-  </si>
-  <si>
-    <t>complete_type</t>
-  </si>
-  <si>
-    <t>complete_flag</t>
-  </si>
-  <si>
-    <t>complete_id</t>
-  </si>
-  <si>
-    <t>complete_required</t>
-  </si>
-  <si>
-    <t>conds</t>
-  </si>
-  <si>
-    <t>actions</t>
-  </si>
-  <si>
-    <t>step_01</t>
-  </si>
-  <si>
-    <t>與xi對話了解情況</t>
-  </si>
-  <si>
-    <t>flag</t>
-  </si>
-  <si>
-    <t>QK01_talk_xi</t>
-  </si>
-  <si>
-    <t>rm QK01_talk_xi</t>
-  </si>
-  <si>
-    <t>step_02</t>
-  </si>
-  <si>
-    <t>前往黑森林，擊殺黑森林的野狼 ({current}/{required})</t>
-  </si>
-  <si>
-    <t>kill</t>
-  </si>
-  <si>
-    <t>wolf</t>
-  </si>
-  <si>
-    <t>step_03</t>
-  </si>
-  <si>
-    <t>收集刀子 ({current}/{required})</t>
-  </si>
-  <si>
-    <t>collect</t>
-  </si>
-  <si>
-    <t>sword_01</t>
-  </si>
-  <si>
-    <t>step_05</t>
-  </si>
-  <si>
-    <t>任務完成，跟 karen 回報任務</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>QX01</t>
-  </si>
-  <si>
-    <t>屠夫的生意經</t>
-  </si>
-  <si>
-    <t>黑森林的野狼氾濫，xi 的肉舖快沒貨了，想找人幫忙獵狼取皮，順便帶個口信給城裡的商人 karen。</t>
-  </si>
-  <si>
-    <t>axe_01</t>
-  </si>
-  <si>
-    <t>set QX01_map</t>
-  </si>
-  <si>
-    <t>rm QX01_map</t>
-  </si>
-  <si>
-    <t>前往黑森林狩獵，擊殺野狼 ({current}/{required})</t>
-  </si>
-  <si>
-    <t>剝下狼皮 ({current}/{required})</t>
-  </si>
-  <si>
-    <t>plet</t>
-  </si>
-  <si>
-    <t>set QX01_karen</t>
-  </si>
-  <si>
-    <t>帶著狼皮去找商人 karen 談談</t>
-  </si>
-  <si>
-    <t>QX01_karen_done</t>
-  </si>
-  <si>
-    <t>step_04</t>
-  </si>
-  <si>
-    <t>任務完成，回去跟 xi 回報</t>
-  </si>
-  <si>
-    <t>QX02</t>
-  </si>
-  <si>
-    <t>跑腿的交涉</t>
-  </si>
-  <si>
-    <t>黑森林的野狼問題解決後，xi 想跟 karen 談長期收購狼皮的生意，請你幫忙帶提案去交涉。</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>set QX02_karen</t>
-  </si>
-  <si>
-    <t>帶著提案去找商人 karen 談交涉條件</t>
-  </si>
-  <si>
-    <t>QX02_karen_done</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>set QX02_s01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rm QX02_s01 ;
+rm QX02_s01_done</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="4">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="微軟正黑體 Light"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="11"/>
-      <name val="微軟正黑體 Light"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -233,7 +260,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -245,7 +272,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -259,16 +286,30 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -304,7 +345,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -640,24 +681,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="57.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -686,7 +728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="63" customHeight="1">
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -704,13 +746,13 @@
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -718,149 +760,151 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:10" ht="31.5" customHeight="1">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="31.5" customHeight="1">
       <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H5" s="5">
         <v>1</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H6" s="5">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J7" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3" style="6" customWidth="1"/>
     <col min="2" max="2" width="10" style="6" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" style="6" customWidth="1"/>
     <col min="4" max="4" width="57.7109375" style="6" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" style="6" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" style="6" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" style="6" customWidth="1"/>
     <col min="9" max="9" width="19.7109375" style="6" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="23.140625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="31.5" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -889,15 +933,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="47.25" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="63" customHeight="1">
       <c r="B2" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E2" s="7">
         <v>120</v>
@@ -906,16 +950,16 @@
         <v>120</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="31.5" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -923,46 +967,46 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:10" ht="31.5" customHeight="1">
+      <c r="B4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H4" s="5">
         <v>3</v>
@@ -970,78 +1014,80 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="B5" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H5" s="5">
         <v>1</v>
       </c>
       <c r="I5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="31.5" customHeight="1">
+      <c r="B6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="5"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="B7" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" ht="35.25" customHeight="1" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="35.25" customHeight="1">
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -1052,7 +1098,7 @@
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
-    <row r="9" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="31.5" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>0</v>
       </c>
@@ -1081,15 +1127,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="47.25" customHeight="1">
       <c r="B10" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E10" s="7">
         <v>100</v>
@@ -1098,14 +1144,14 @@
         <v>100</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="31.5" customHeight="1">
       <c r="A11" s="6" t="s">
         <v>0</v>
       </c>
@@ -1113,74 +1159,77 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="4" t="s">
+    </row>
+    <row r="12" spans="1:10" ht="32.25" customHeight="1">
+      <c r="B12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" ht="32.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="F12" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
       <c r="B13" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J13" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -77,16 +77,10 @@
     <t>step_01</t>
   </si>
   <si>
-    <t>與xi對話了解情況</t>
-  </si>
-  <si>
     <t>flag</t>
   </si>
   <si>
     <t>step_02</t>
-  </si>
-  <si>
-    <t>前往黑森林，擊殺黑森林的野狼 ({current}/{required})</t>
   </si>
   <si>
     <t>kill</t>
@@ -209,6 +203,30 @@
   <si>
     <t>rm QX02_s01 ;
 rm QX02_s01_done</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pos</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>前往黑森林，擊殺黑森林的野狼 ({current}/{required})</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>step_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>與xi對話了解情況</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>step_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>forest-01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -246,7 +264,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -274,6 +292,12 @@
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -317,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -340,8 +364,14 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -682,24 +712,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="4" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="57.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.5" customHeight="1">
+    <row r="1" spans="1:11" ht="31.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -728,31 +758,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="63" customHeight="1">
+    <row r="2" spans="1:11" ht="31.5">
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="7">
         <v>100</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="7">
         <v>100</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="7"/>
+      <c r="H2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="31.5" customHeight="1">
+    </row>
+    <row r="3" spans="1:11" ht="31.5">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -783,46 +813,50 @@
       <c r="J3" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="31.5" customHeight="1">
+      <c r="K3" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="31.5">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="31.5" customHeight="1">
+        <v>54</v>
+      </c>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" spans="1:11">
       <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H5" s="5">
         <v>1</v>
@@ -831,81 +865,86 @@
         <v>19</v>
       </c>
       <c r="J5" s="5"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K5" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H6" s="5">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J6" s="5"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="1:11">
       <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J7" s="5"/>
+      <c r="K7" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3" style="6" customWidth="1"/>
-    <col min="2" max="2" width="10" style="6" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="57.7109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="6" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" style="6" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="6" customWidth="1"/>
-    <col min="10" max="10" width="23.140625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="3" style="8" customWidth="1"/>
+    <col min="2" max="2" width="10" style="8" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="8" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" style="8" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="8" customWidth="1"/>
+    <col min="10" max="10" width="23.140625" style="8" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:11" ht="31.5" customHeight="1">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -933,15 +972,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="63" customHeight="1">
+    <row r="2" spans="1:11" ht="63" customHeight="1">
       <c r="B2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="E2" s="7">
         <v>120</v>
@@ -950,17 +989,17 @@
         <v>120</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A3" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="31.5" customHeight="1">
+      <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -990,46 +1029,52 @@
       <c r="J3" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="31.5" customHeight="1">
+      <c r="K3" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="31.5" customHeight="1">
       <c r="B4" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H4" s="5">
         <v>3</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K4" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" customHeight="1">
       <c r="B5" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H5" s="5">
         <v>1</v>
@@ -1038,68 +1083,71 @@
         <v>19</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="31.5" customHeight="1">
+        <v>48</v>
+      </c>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" ht="31.5" customHeight="1">
       <c r="B6" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+        <v>50</v>
+      </c>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" customHeight="1">
       <c r="B7" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J7" s="5"/>
-    </row>
-    <row r="8" spans="1:10" ht="35.25" customHeight="1">
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="1:11" s="6" customFormat="1">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="31.5" customHeight="1">
+      <c r="A9" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1127,15 +1175,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="47.25" customHeight="1">
+    <row r="10" spans="1:11" ht="47.25" customHeight="1">
       <c r="B10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="E10" s="7">
         <v>100</v>
@@ -1144,15 +1192,15 @@
         <v>100</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:11" ht="31.5" customHeight="1">
+      <c r="A11" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1182,42 +1230,46 @@
       <c r="J11" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="32.25" customHeight="1">
+      <c r="K11" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="32.25" customHeight="1">
       <c r="B12" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+        <v>57</v>
+      </c>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" customHeight="1">
       <c r="B13" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -1226,6 +1278,7 @@
         <v>19</v>
       </c>
       <c r="J13" s="5"/>
+      <c r="K13" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/xls/quest.xlsx
+++ b/xls/quest.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="585" windowWidth="12615" windowHeight="6750" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="karen" sheetId="1" r:id="rId1"/>
-    <sheet name="xi" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="karen" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="xi" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="62">
   <si>
     <t>#</t>
   </si>
@@ -53,6 +53,13 @@
     <t>黑森林的野狼越來越猖獗，長老需要你的幫助。</t>
   </si>
   <si>
+    <t xml:space="preserve">set QK01_s01 ;
+set QK01_map</t>
+  </si>
+  <si>
+    <t>rm QK01_map</t>
+  </si>
+  <si>
     <t>step_id</t>
   </si>
   <si>
@@ -74,21 +81,40 @@
     <t>actions</t>
   </si>
   <si>
+    <t>pos</t>
+  </si>
+  <si>
     <t>step_01</t>
   </si>
   <si>
+    <t>與xi對話了解情況</t>
+  </si>
+  <si>
     <t>flag</t>
   </si>
   <si>
+    <t>QK01_s01_done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rm QK01_s01 ;
+rm QK01_s01_done</t>
+  </si>
+  <si>
     <t>step_02</t>
   </si>
   <si>
+    <t>前往黑森林，擊殺黑森林的野狼 ({current}/{required})</t>
+  </si>
+  <si>
     <t>kill</t>
   </si>
   <si>
     <t>wolf</t>
   </si>
   <si>
+    <t>m/m_03x05</t>
+  </si>
+  <si>
     <t>step_03</t>
   </si>
   <si>
@@ -125,6 +151,9 @@
     <t>set QX01_map</t>
   </si>
   <si>
+    <t>rm QX01_map</t>
+  </si>
+  <si>
     <t>前往黑森林狩獵，擊殺野狼 ({current}/{required})</t>
   </si>
   <si>
@@ -134,9 +163,19 @@
     <t>plet</t>
   </si>
   <si>
+    <t>set QX01_s03</t>
+  </si>
+  <si>
     <t>帶著狼皮去找商人 karen 談談</t>
   </si>
   <si>
+    <t>QX01_s03_done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rm QX01_s03 ;
+rm QX01_s03_done</t>
+  </si>
+  <si>
     <t>step_04</t>
   </si>
   <si>
@@ -155,113 +194,44 @@
     <t/>
   </si>
   <si>
+    <t>set QX02_s01</t>
+  </si>
+  <si>
     <t>帶著提案去找商人 karen 談交涉條件</t>
   </si>
   <si>
     <t>QX02_s01_done</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>set QX01_s03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>QX01_s03_done</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>rm QX01_s03 ;
-rm QX01_s03_done</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>rm QX01_map</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>QK01_s01_done</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>set QK01_s01 ;
-set QK01_map</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>rm QK01_s01 ;
-rm QK01_s01_done</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>rm QK01_map</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>set QX02_s01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>rm QX02_s01 ;
+  </si>
+  <si>
+    <t xml:space="preserve">rm QX02_s01 ;
 rm QX02_s01_done</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>pos</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>前往黑森林，擊殺黑森林的野狼 ({current}/{required})</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>step_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>與xi對話了解情況</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>step_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>forest-01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="微軟正黑體 Light"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="微軟正黑體 Light"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -278,7 +248,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -290,13 +260,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,30 +280,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -352,30 +308,30 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -711,25 +667,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="59.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.85546875" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.5">
+    <row r="1" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -758,193 +714,192 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="31.5">
+    <row r="2" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="4">
         <v>100</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="4">
         <v>100</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="31.5">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="31.5">
-      <c r="B4" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K4" s="10"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="B5" s="5" t="s">
+      <c r="C4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="J5" s="7"/>
+      <c r="K5" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="7">
         <v>1</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="B6" s="5" t="s">
+      <c r="I6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="7"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="10"/>
+      <c r="C7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3" style="8" customWidth="1"/>
-    <col min="2" max="2" width="10" style="8" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="57.7109375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="8" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" style="8" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="8" customWidth="1"/>
-    <col min="10" max="10" width="23.140625" style="8" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" style="8" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="3" style="9" customWidth="1"/>
+    <col min="2" max="2" width="10" style="9" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="9" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="23.140625" style="9" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" style="9" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.5" customHeight="1">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -972,170 +927,170 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="63" customHeight="1">
-      <c r="B2" s="7" t="s">
+    <row r="2" ht="63" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="4">
+        <v>120</v>
+      </c>
+      <c r="F2" s="4">
+        <v>120</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="7">
+        <v>3</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="5" ht="15.75" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="7">
-        <v>120</v>
-      </c>
-      <c r="F2" s="7">
-        <v>120</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="7" t="s">
+      <c r="D6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="31.5" customHeight="1">
-      <c r="A3" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="31.5" customHeight="1">
-      <c r="B4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="5">
-        <v>3</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1">
-      <c r="B5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" spans="1:11" ht="31.5" customHeight="1">
-      <c r="B6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1">
-      <c r="B7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8" spans="1:11" s="6" customFormat="1">
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -1146,8 +1101,8 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="31.5" customHeight="1">
-      <c r="A9" s="8" t="s">
+    <row r="9" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1175,114 +1130,113 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="47.25" customHeight="1">
-      <c r="B10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="7">
+    <row r="10" ht="47.25" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="4">
         <v>100</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="4">
         <v>100</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:11" ht="31.5" customHeight="1">
-      <c r="A11" s="8" t="s">
+      <c r="G10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="32.25" customHeight="1">
-      <c r="B12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="J11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1">
-      <c r="B13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="K11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="10"/>
+    </row>
+    <row r="12" ht="32.25" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>